--- a/apps/api/tests/debug-export.xlsx
+++ b/apps/api/tests/debug-export.xlsx
@@ -20,7 +20,7 @@
     <t>TCOS Activity Report — Improv Workshop</t>
   </si>
   <si>
-    <t>Exported: 22/5/2569 20:53:04  |  Price: ฿500  |  Capacity: 30</t>
+    <t>Exported: 22/5/2569 21:06:56  |  Price: ฿500  |  Capacity: 30</t>
   </si>
   <si>
     <t>Metric</t>

--- a/apps/api/tests/debug-export.xlsx
+++ b/apps/api/tests/debug-export.xlsx
@@ -20,7 +20,7 @@
     <t>TCOS Activity Report — Improv Workshop</t>
   </si>
   <si>
-    <t>Exported: 22/5/2569 21:06:56  |  Price: ฿500  |  Capacity: 30</t>
+    <t>Exported: 30/5/2569 16:29:03  |  Price: ฿500  |  Capacity: 30</t>
   </si>
   <si>
     <t>Metric</t>

--- a/apps/api/tests/debug-export.xlsx
+++ b/apps/api/tests/debug-export.xlsx
@@ -20,7 +20,7 @@
     <t>TCOS Activity Report — Improv Workshop</t>
   </si>
   <si>
-    <t>Exported: 30/5/2569 16:29:03  |  Price: ฿500  |  Capacity: 30</t>
+    <t>Exported: 2/6/2569 15:33:09  |  Price: ฿500  |  Capacity: 30</t>
   </si>
   <si>
     <t>Metric</t>

--- a/apps/api/tests/debug-export.xlsx
+++ b/apps/api/tests/debug-export.xlsx
@@ -20,7 +20,7 @@
     <t>TCOS Activity Report — Improv Workshop</t>
   </si>
   <si>
-    <t>Exported: 2/6/2569 15:33:09  |  Price: ฿500  |  Capacity: 30</t>
+    <t>Exported: 2/6/2569 22:48:29  |  Price: ฿500  |  Capacity: 30</t>
   </si>
   <si>
     <t>Metric</t>

--- a/apps/api/tests/debug-export.xlsx
+++ b/apps/api/tests/debug-export.xlsx
@@ -20,7 +20,7 @@
     <t>TCOS Activity Report — Improv Workshop</t>
   </si>
   <si>
-    <t>Exported: 2/6/2569 22:48:29  |  Price: ฿500  |  Capacity: 30</t>
+    <t>Exported: 3/6/2569 20:21:35  |  Price: ฿500  |  Capacity: 30</t>
   </si>
   <si>
     <t>Metric</t>

--- a/apps/api/tests/debug-export.xlsx
+++ b/apps/api/tests/debug-export.xlsx
@@ -20,7 +20,7 @@
     <t>TCOS Activity Report — Improv Workshop</t>
   </si>
   <si>
-    <t>Exported: 3/6/2569 20:21:35  |  Price: ฿500  |  Capacity: 30</t>
+    <t>Exported: 5/6/2569 18:35:32  |  Price: ฿500  |  Capacity: 30</t>
   </si>
   <si>
     <t>Metric</t>
